--- a/data/organelle_interaction_data.xlsx
+++ b/data/organelle_interaction_data.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.01990329807038792</v>
+        <v>0.01172474304588331</v>
       </c>
       <c r="D2" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1216603461565424</v>
+        <v>0.0647938453137991</v>
       </c>
       <c r="D3" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.01215106394721442</v>
+        <v>0.005520966348984243</v>
       </c>
       <c r="D4" t="n">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5">
@@ -503,10 +503,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.00123405919284404</v>
+        <v>0.0005564414123770027</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.008649037615163604</v>
+        <v>0.005639198905345899</v>
       </c>
       <c r="D6" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7">
@@ -535,10 +535,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.02176914041986759</v>
+        <v>0.00068536548231565</v>
       </c>
       <c r="D7" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -551,10 +551,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.001965836327036992</v>
+        <v>0.001755980112223938</v>
       </c>
       <c r="D8" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.02065299664560794</v>
+        <v>0.01435956682420854</v>
       </c>
       <c r="D9" t="n">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.002413058252975662</v>
+        <v>0.0009750196264085028</v>
       </c>
       <c r="D10" t="n">
-        <v>28</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.09296765268391319</v>
+        <v>0.004643026777286495</v>
       </c>
       <c r="D11" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12">
@@ -615,10 +615,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.02587036653269734</v>
+        <v>0.01987042077218099</v>
       </c>
       <c r="D12" t="n">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13">
@@ -631,10 +631,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.002585989682394783</v>
+        <v>0.0005807533258015492</v>
       </c>
       <c r="D13" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.0004040981333128117</v>
+        <v>9.21028896543119e-05</v>
       </c>
       <c r="D14" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.001826024462109777</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -682,7 +682,7 @@
         <v>0.0001090611472652376</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="17">
@@ -695,10 +695,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.0008544983611530288</v>
+        <v>0.0007640258439189027</v>
       </c>
       <c r="D17" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.003002084936593828</v>
+        <v>0.002739406719652824</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.0002897421000583335</v>
+        <v>0.0001985085683834987</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -743,10 +743,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.006240730817406917</v>
+        <v>0.0003454325505733986</v>
       </c>
       <c r="D20" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.006338000531511748</v>
+        <v>0.0007880798365835709</v>
       </c>
       <c r="D21" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22">
@@ -775,10 +775,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.0005922908525300053</v>
+        <v>0.0005419243324635615</v>
       </c>
       <c r="D22" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23">
@@ -791,10 +791,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.00651957212884301</v>
+        <v>0.004639501049382206</v>
       </c>
       <c r="D23" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.003208217740963049</v>
+        <v>0.002513126456248268</v>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="26">
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.002913982403284886</v>
+        <v>0.0009252863576899435</v>
       </c>
       <c r="D27" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
     </row>
     <row r="28">
@@ -871,10 +871,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.03221198497509453</v>
+        <v>0.004408704368129643</v>
       </c>
       <c r="D28" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.001220197719977037</v>
+        <v>0.0001283948928816134</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
@@ -903,10 +903,10 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.001667818144741072</v>
+        <v>0.001408322877953901</v>
       </c>
       <c r="D30" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.0007427136729897145</v>
+        <v>0.0006541710062170506</v>
       </c>
       <c r="D31" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -935,10 +935,10 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.001616488457308767</v>
+        <v>0.001398603726395266</v>
       </c>
       <c r="D32" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33">
@@ -967,10 +967,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.006740249477499269</v>
+        <v>0.002107392556379668</v>
       </c>
       <c r="D34" t="n">
-        <v>98</v>
+        <v>20</v>
       </c>
     </row>
     <row r="35">
@@ -983,10 +983,10 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.004151237930907168</v>
+        <v>0.00377460648837801</v>
       </c>
       <c r="D35" t="n">
-        <v>83</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.0001484714855515156</v>
+        <v>0.0001131156645754276</v>
       </c>
       <c r="D37" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.0003629820404622257</v>
+        <v>6.846306629991224e-06</v>
       </c>
       <c r="D38" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.001605887145775039</v>
+        <v>0.000328395252019431</v>
       </c>
       <c r="D40" t="n">
-        <v>44</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -1079,10 +1079,10 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.0009381157395164866</v>
+        <v>0.0001120982410533533</v>
       </c>
       <c r="D41" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42">
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3.599423976416212e-05</v>
+        <v>3.833969405176779e-05</v>
       </c>
       <c r="D43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -1159,10 +1159,10 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.003352379709642529</v>
+        <v>0.0003208022438855837</v>
       </c>
       <c r="D46" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47">
@@ -1207,10 +1207,10 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.000495660199660809</v>
+        <v>0.0003214324136994744</v>
       </c>
       <c r="D49" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.02165286143757064</v>
+        <v>0.0005788574017196987</v>
       </c>
       <c r="D50" t="n">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="51">
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.00132910976985948</v>
+        <v>0.00125258732383044</v>
       </c>
       <c r="D52" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0008670366586210198</v>
+        <v>0.0002836764130180001</v>
       </c>
       <c r="D53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54">
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.00064616153413189</v>
+        <v>0.0003185927976052354</v>
       </c>
       <c r="D56" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
